--- a/docs/ESP32S3_PlantMonitor_RevA_BOM.xlsx
+++ b/docs/ESP32S3_PlantMonitor_RevA_BOM.xlsx
@@ -1625,12 +1625,12 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>0603WAF1002T5E</t>
+          <t>RC0603FR-0710KL</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>C25804</t>
+          <t>C98220</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>Stock was 0 on 2026-07-20 - re-check; alternate: YAGEO RC0603FR-0710KL = C98220 (Extended)</t>
+          <t>Stock was 0 on 2026-07-20 - re-check; alternate: YAGEO RC0603FR-0710KL = C98220 (Extended) | was C25804 (Uni-Royal, Basic) — JLC pre-order failed 2026-08-18, switched to Yageo C98220</t>
         </is>
       </c>
     </row>
@@ -2127,6 +2127,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="B34" s="10" t="inlineStr">
         <is>
